--- a/presupuesto_TMK.xlsx
+++ b/presupuesto_TMK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/07 Julio/tmk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/08 Agosto/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="307" documentId="11_E95008F7534E980F6235547658484EBB89F0B472" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64A6D948-843C-4632-A0F8-40F80B4B6609}"/>
+  <xr:revisionPtr revIDLastSave="321" documentId="11_E95008F7534E980F6235547658484EBB89F0B472" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66E8C60A-A02E-4EBC-855F-1DDFBA51944C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="28">
   <si>
     <t>Año</t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>Julio</t>
+  </si>
+  <si>
+    <t>Agosto</t>
   </si>
 </sst>
 </file>
@@ -502,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
@@ -2458,6 +2461,222 @@
         <v>1.52</v>
       </c>
     </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>2026</v>
+      </c>
+      <c r="B70" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70">
+        <v>75</v>
+      </c>
+      <c r="G70">
+        <v>42</v>
+      </c>
+      <c r="H70" s="5">
+        <f t="shared" ref="H70:H77" si="7">G70/F70</f>
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>2026</v>
+      </c>
+      <c r="B71" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71">
+        <v>150</v>
+      </c>
+      <c r="G71">
+        <v>141</v>
+      </c>
+      <c r="H71" s="5">
+        <f t="shared" si="7"/>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2026</v>
+      </c>
+      <c r="B72" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72">
+        <v>60</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2026</v>
+      </c>
+      <c r="B73" t="s">
+        <v>27</v>
+      </c>
+      <c r="C73" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="4">
+        <v>100000</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2026</v>
+      </c>
+      <c r="B74" t="s">
+        <v>27</v>
+      </c>
+      <c r="C74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" t="s">
+        <v>18</v>
+      </c>
+      <c r="F74">
+        <v>25</v>
+      </c>
+      <c r="G74">
+        <v>23</v>
+      </c>
+      <c r="H74" s="5">
+        <f t="shared" si="7"/>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>2026</v>
+      </c>
+      <c r="B75" t="s">
+        <v>27</v>
+      </c>
+      <c r="C75" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" t="s">
+        <v>18</v>
+      </c>
+      <c r="F75">
+        <v>50</v>
+      </c>
+      <c r="G75">
+        <v>69</v>
+      </c>
+      <c r="H75" s="5">
+        <f t="shared" si="7"/>
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>2026</v>
+      </c>
+      <c r="B76" t="s">
+        <v>27</v>
+      </c>
+      <c r="C76" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" t="s">
+        <v>17</v>
+      </c>
+      <c r="E76" t="s">
+        <v>20</v>
+      </c>
+      <c r="F76">
+        <v>25</v>
+      </c>
+      <c r="G76">
+        <v>16</v>
+      </c>
+      <c r="H76" s="5">
+        <f t="shared" si="7"/>
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>2026</v>
+      </c>
+      <c r="B77" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" t="s">
+        <v>20</v>
+      </c>
+      <c r="F77">
+        <v>50</v>
+      </c>
+      <c r="G77">
+        <v>68</v>
+      </c>
+      <c r="H77" s="5">
+        <f t="shared" si="7"/>
+        <v>1.36</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I69" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/presupuesto_TMK.xlsx
+++ b/presupuesto_TMK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/08 Agosto/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="321" documentId="11_E95008F7534E980F6235547658484EBB89F0B472" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66E8C60A-A02E-4EBC-855F-1DDFBA51944C}"/>
+  <xr:revisionPtr revIDLastSave="331" documentId="11_E95008F7534E980F6235547658484EBB89F0B472" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7B0C99F-5463-40B3-B665-323767444A48}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos!$A$1:$I$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos!$A$1:$I$77</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -2478,14 +2478,14 @@
         <v>12</v>
       </c>
       <c r="F70">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="G70">
         <v>42</v>
       </c>
       <c r="H70" s="5">
         <f t="shared" ref="H70:H77" si="7">G70/F70</f>
-        <v>0.56000000000000005</v>
+        <v>0.93333333333333335</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -2640,14 +2640,14 @@
         <v>20</v>
       </c>
       <c r="F76">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G76">
         <v>16</v>
       </c>
       <c r="H76" s="5">
         <f t="shared" si="7"/>
-        <v>0.64</v>
+        <v>1.0666666666666667</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -2667,18 +2667,18 @@
         <v>20</v>
       </c>
       <c r="F77">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G77">
         <v>68</v>
       </c>
       <c r="H77" s="5">
         <f t="shared" si="7"/>
-        <v>1.36</v>
+        <v>0.97142857142857142</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I69" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/presupuesto_TMK.xlsx
+++ b/presupuesto_TMK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/08 Agosto/tmk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/09 Septiembre/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="331" documentId="11_E95008F7534E980F6235547658484EBB89F0B472" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7B0C99F-5463-40B3-B665-323767444A48}"/>
+  <xr:revisionPtr revIDLastSave="342" documentId="11_E95008F7534E980F6235547658484EBB89F0B472" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{160FB302-337A-4150-A6E0-979AC10E7231}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="29">
   <si>
     <t>Año</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>Agosto</t>
+  </si>
+  <si>
+    <t>Septiembre</t>
   </si>
 </sst>
 </file>
@@ -505,9 +508,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -2677,6 +2681,222 @@
         <v>0.97142857142857142</v>
       </c>
     </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>2026</v>
+      </c>
+      <c r="B78" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78">
+        <v>45</v>
+      </c>
+      <c r="G78">
+        <v>46</v>
+      </c>
+      <c r="H78" s="5">
+        <f>G78/F78</f>
+        <v>1.0222222222222221</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>2026</v>
+      </c>
+      <c r="B79" t="s">
+        <v>28</v>
+      </c>
+      <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79">
+        <v>150</v>
+      </c>
+      <c r="G79">
+        <v>157</v>
+      </c>
+      <c r="H79" s="5">
+        <f t="shared" ref="H79:H85" si="8">G79/F79</f>
+        <v>1.0466666666666666</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>2026</v>
+      </c>
+      <c r="B80" t="s">
+        <v>28</v>
+      </c>
+      <c r="C80" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80">
+        <v>60</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80" s="5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>2026</v>
+      </c>
+      <c r="B81" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81">
+        <v>100000</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81" s="5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>2026</v>
+      </c>
+      <c r="B82" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82" t="s">
+        <v>18</v>
+      </c>
+      <c r="F82">
+        <v>25</v>
+      </c>
+      <c r="G82">
+        <v>28</v>
+      </c>
+      <c r="H82" s="5">
+        <f t="shared" si="8"/>
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>2026</v>
+      </c>
+      <c r="B83" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" t="s">
+        <v>18</v>
+      </c>
+      <c r="F83">
+        <v>50</v>
+      </c>
+      <c r="G83">
+        <v>66</v>
+      </c>
+      <c r="H83" s="5">
+        <f t="shared" si="8"/>
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>2026</v>
+      </c>
+      <c r="B84" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84" t="s">
+        <v>20</v>
+      </c>
+      <c r="F84">
+        <v>15</v>
+      </c>
+      <c r="G84">
+        <v>16</v>
+      </c>
+      <c r="H84" s="5">
+        <f t="shared" si="8"/>
+        <v>1.0666666666666667</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>2026</v>
+      </c>
+      <c r="B85" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" t="s">
+        <v>20</v>
+      </c>
+      <c r="F85">
+        <v>70</v>
+      </c>
+      <c r="G85">
+        <v>92</v>
+      </c>
+      <c r="H85" s="5">
+        <f t="shared" si="8"/>
+        <v>1.3142857142857143</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
